--- a/docs/assets/RetirementPlanning.xlsx
+++ b/docs/assets/RetirementPlanning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerry\repos\mgmt675-2025\docs\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33179396-9E62-4869-B282-6F97091F3705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A492B7-4B28-4FD5-AAA4-BC7FB2275D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{5C29E880-E3A5-44DA-98FE-8F91E021F464}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{5C29E880-E3A5-44DA-98FE-8F91E021F464}"/>
   </bookViews>
   <sheets>
     <sheet name="Constant" sheetId="2" r:id="rId1"/>
@@ -223,7 +223,7 @@
     <cellStyle name="Output" xfId="4" builtinId="21"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="13">
     <dxf>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -235,9 +235,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -408,18 +405,18 @@
   <autoFilter ref="A6:E16" xr:uid="{3F88EBF6-636E-45E1-A392-C661F36E012D}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7409C94A-E697-44C7-9D7E-C22F02F76AF0}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{ACC4C547-200E-4737-9F27-48D670883547}" name="Beginning Balance" totalsRowFunction="custom" dataDxfId="13">
+    <tableColumn id="2" xr3:uid="{ACC4C547-200E-4737-9F27-48D670883547}" name="Beginning Balance" totalsRowFunction="custom" dataDxfId="12">
       <totalsRowFormula>_xlfn.FORMULATEXT(B16)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4EAF096E-91B3-4FED-B23F-1A6FBF35BFF6}" name="Return" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="11">
+    <tableColumn id="3" xr3:uid="{4EAF096E-91B3-4FED-B23F-1A6FBF35BFF6}" name="Return" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>$B$1</calculatedColumnFormula>
       <totalsRowFormula>_xlfn.FORMULATEXT(C16)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1C165765-58F8-404F-94FF-0449D6E68EF0}" name="Gain (Loss)" totalsRowFunction="custom" dataDxfId="10" totalsRowDxfId="9">
+    <tableColumn id="4" xr3:uid="{1C165765-58F8-404F-94FF-0449D6E68EF0}" name="Gain (Loss)" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>Table13[[#This Row],[Beginning Balance]]*Table13[[#This Row],[Return]]</calculatedColumnFormula>
       <totalsRowFormula>_xlfn.FORMULATEXT(D7)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62C0FD09-0B7C-48C9-B28E-12B5C3C01821}" name="Deposit (Withdrawal)" dataDxfId="8" totalsRowDxfId="7">
+    <tableColumn id="5" xr3:uid="{62C0FD09-0B7C-48C9-B28E-12B5C3C01821}" name="Deposit (Withdrawal)" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>$B$3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -432,16 +429,15 @@
   <autoFilter ref="A8:E18" xr:uid="{3F88EBF6-636E-45E1-A392-C661F36E012D}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9A8E175F-484A-45B5-9D47-DA340692B21E}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{5650B33B-0DC4-44AC-95CB-32E7016ED274}" name="Beginning Balance" totalsRowFunction="custom" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{5650B33B-0DC4-44AC-95CB-32E7016ED274}" name="Beginning Balance" totalsRowFunction="custom" dataDxfId="5">
       <totalsRowFormula>_xlfn.FORMULATEXT(B18)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{79539066-3D2A-4F18-B9B6-23FF6E702527}" name="Return" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="3" xr3:uid="{79539066-3D2A-4F18-B9B6-23FF6E702527}" name="Return" totalsRowFunction="custom" dataDxfId="4">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</calculatedColumnFormula>
       <totalsRowFormula>_xlfn.FORMULATEXT(C18)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08A68FFD-6E75-444F-B6D2-A3505D036DD3}" name="Gain (Loss)" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="4" xr3:uid="{08A68FFD-6E75-444F-B6D2-A3505D036DD3}" name="Gain (Loss)" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</calculatedColumnFormula>
-      <totalsRowFormula>_xlfn.FORMULATEXT(D9)</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{32BA16FB-FDEB-462E-8343-1FE1469F03C9}" name="Deposit (Withdrawal)" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>$B$4</calculatedColumnFormula>
@@ -1166,11 +1162,11 @@
       </c>
       <c r="C9">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.1937225788175708</v>
+        <v>0.20185676302651964</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>9686.1289408785397</v>
+        <v>10092.838151325983</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" ref="E9:E13" si="0">$B$4</f>
@@ -1183,15 +1179,15 @@
       </c>
       <c r="B10" s="3">
         <f ca="1">B9+D9+E9</f>
-        <v>69686.128940878538</v>
+        <v>70092.838151325981</v>
       </c>
       <c r="C10">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.11818907640145628</v>
+        <v>0.21577482023248956</v>
       </c>
       <c r="D10" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>8236.1392175152268</v>
+        <v>15124.26955168735</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
@@ -1204,15 +1200,15 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:B18" ca="1" si="1">B10+D10+E10</f>
-        <v>87922.268158393766</v>
+        <v>95217.107703013331</v>
       </c>
       <c r="C11">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.11658306975900531</v>
+        <v>3.797110526617721E-2</v>
       </c>
       <c r="D11" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>10250.247922079992</v>
+        <v>3615.4988197320522</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
@@ -1225,15 +1221,15 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>108172.51608047375</v>
+        <v>108832.60652274538</v>
       </c>
       <c r="C12">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>9.2251242334983552E-2</v>
+        <v>0.21853646748555672</v>
       </c>
       <c r="D12" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>9979.0489949246894</v>
+        <v>23783.893376726333</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
@@ -1246,15 +1242,15 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>128151.56507539844</v>
+        <v>142616.4998994717</v>
       </c>
       <c r="C13">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.51979829770178376</v>
+        <v>-0.34386978765110932</v>
       </c>
       <c r="D13" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>66612.965374011474</v>
+        <v>-49041.50553597579</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
@@ -1267,15 +1263,15 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>204764.53044940991</v>
+        <v>103574.99436349591</v>
       </c>
       <c r="C14">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.11112905439480462</v>
+        <v>0.40125180389853798</v>
       </c>
       <c r="D14" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>22755.288642439104</v>
+        <v>41559.653327133638</v>
       </c>
       <c r="E14" s="3">
         <f>-$B$5</f>
@@ -1288,15 +1284,15 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>192519.81909184903</v>
+        <v>110134.64769062953</v>
       </c>
       <c r="C15">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>-0.17841391976643053</v>
+        <v>-0.24068485399369446</v>
       </c>
       <c r="D15" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>-34348.215556900876</v>
+        <v>-26507.741599066147</v>
       </c>
       <c r="E15" s="3">
         <f>-$B$5</f>
@@ -1309,15 +1305,15 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>123171.60353494814</v>
+        <v>48626.906091563375</v>
       </c>
       <c r="C16">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>0.50748058904602511</v>
+        <v>-0.23985113973633407</v>
       </c>
       <c r="D16" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>62507.197915658951</v>
+        <v>-11663.218847913162</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" ref="E16:E18" si="2">-$B$5</f>
@@ -1330,15 +1326,15 @@
       </c>
       <c r="B17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>150678.80145060708</v>
+        <v>1963.6872436502163</v>
       </c>
       <c r="C17">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>5.9650166804658733E-2</v>
+        <v>8.6930754697406631E-2</v>
       </c>
       <c r="D17" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>8988.015640454767</v>
+        <v>170.70481408018352</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="2"/>
@@ -1351,15 +1347,15 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>124666.81709106185</v>
+        <v>-32865.607942269598</v>
       </c>
       <c r="C18">
         <f ca="1">IF(Table1[[#This Row],[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</f>
-        <v>-0.13080234406365143</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="3">
         <f ca="1">Table1[[#This Row],[Beginning Balance]]*Table1[[#This Row],[Return]]</f>
-        <v>-16306.711902465373</v>
+        <v>-3286.5607942269598</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="2"/>
@@ -1375,10 +1371,7 @@
         <f ca="1">_xlfn.FORMULATEXT(C18)</f>
         <v>=IF([@[Beginning Balance]]&gt;0, NORMINV(RAND(), $B$1, $B$2), $B$6)</v>
       </c>
-      <c r="D19" s="3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D9)</f>
-        <v>=[@[Beginning Balance]]*[@Return]</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -1387,7 +1380,7 @@
       </c>
       <c r="B20" s="5">
         <f ca="1">B18+D18+E18</f>
-        <v>73360.10518859647</v>
+        <v>-71152.168736496562</v>
       </c>
     </row>
   </sheetData>
